--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_5.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_5.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Anxiety</t>
+          <t>SelfConfidenceRating</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Perfectionism</t>
+          <t>SelfConfidence</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-1.205309761974958</v>
+        <v>2.258402241988122</v>
       </c>
       <c r="C2">
-        <v>-0.1843425512030046</v>
+        <v>0.1139056497257503</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.030772249324551</v>
+        <v>0.1892128891419206</v>
       </c>
       <c r="C3">
-        <v>-0.4415685975509717</v>
+        <v>0.357635985702354</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.5785359802737621</v>
+        <v>1.105702398567637</v>
       </c>
       <c r="C4">
-        <v>-0.6881238361681902</v>
+        <v>1.350885163509949</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-1.317876482266908</v>
+        <v>0.8484396756942428</v>
       </c>
       <c r="C5">
-        <v>0.07450996732882961</v>
+        <v>-0.07638850899780325</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.4695591182478869</v>
+        <v>0.3142027253645182</v>
       </c>
       <c r="C6">
-        <v>-0.455330110286555</v>
+        <v>-2.163517653888802</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.2551590066067327</v>
+        <v>-0.9024756288329541</v>
       </c>
       <c r="C7">
-        <v>1.177904906115083</v>
+        <v>0.3233316943017067</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-3.101442357311996</v>
+        <v>0.2714198137666347</v>
       </c>
       <c r="C8">
-        <v>-0.6818578457711695</v>
+        <v>0.6320624581906875</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.1983729704697843</v>
+        <v>1.024244939165388</v>
       </c>
       <c r="C9">
-        <v>-0.2232288331307513</v>
+        <v>0.7693174413536972</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.493884945899234</v>
+        <v>-0.5319708842303034</v>
       </c>
       <c r="C10">
-        <v>1.167947486396868</v>
+        <v>-0.9405479473823</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.06921264351506928</v>
+        <v>0.2174180371109492</v>
       </c>
       <c r="C11">
-        <v>0.5699880646709318</v>
+        <v>1.351282469854522</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-1.38502118813821</v>
+        <v>0.2328684094491168</v>
       </c>
       <c r="C12">
-        <v>-0.211202280884734</v>
+        <v>0.07418023513465392</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-2.285876458424408</v>
+        <v>0.2147427740770114</v>
       </c>
       <c r="C13">
-        <v>1.49282866032725</v>
+        <v>-0.8941836385750283</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.1770128333266759</v>
+        <v>-0.09428935813179255</v>
       </c>
       <c r="C14">
-        <v>-1.31286466769578</v>
+        <v>-0.366615510434966</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-1.11499510243511</v>
+        <v>0.4927904808757789</v>
       </c>
       <c r="C15">
-        <v>-1.080238017814347</v>
+        <v>0.1199357728927423</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.01600204352995994</v>
+        <v>0.311892412433059</v>
       </c>
       <c r="C16">
-        <v>1.850663629128303</v>
+        <v>1.37785227713797</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-1.69220436455213</v>
+        <v>1.697930430048993</v>
       </c>
       <c r="C17">
-        <v>-0.5330552111635293</v>
+        <v>1.256563752613065</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-2.469383976516358</v>
+        <v>-0.007090956890860607</v>
       </c>
       <c r="C18">
-        <v>-0.2586752441615064</v>
+        <v>0.2284838572326906</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>1.303233636086944</v>
+        <v>-0.9665113938134317</v>
       </c>
       <c r="C19">
-        <v>-0.8625518600087072</v>
+        <v>-0.5173131460896907</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>1.671893784670193</v>
+        <v>1.250952160145961</v>
       </c>
       <c r="C20">
-        <v>-0.5149426572541761</v>
+        <v>-0.4414993836676261</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>-0.494042351938214</v>
+        <v>-1.69212533480277</v>
       </c>
       <c r="C21">
-        <v>-0.9479960965183327</v>
+        <v>-0.2857252571179019</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-2.034061548065595</v>
+        <v>1.190888429709882</v>
       </c>
       <c r="C22">
-        <v>0.8970144185519738</v>
+        <v>1.172036890818673</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>2.15331447199107</v>
+        <v>-0.3324944493177598</v>
       </c>
       <c r="C23">
-        <v>-0.5424653759874647</v>
+        <v>-1.797276955116065</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.9229115285013918</v>
+        <v>0.3154297942227861</v>
       </c>
       <c r="C24">
-        <v>0.4817719987226381</v>
+        <v>1.041996204357335</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.3024621966751328</v>
+        <v>-0.6475752658551915</v>
       </c>
       <c r="C25">
-        <v>-1.71297563424754</v>
+        <v>-1.829390762548849</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.4380694014447842</v>
+        <v>-0.4276422401786142</v>
       </c>
       <c r="C26">
-        <v>-0.1063706061614448</v>
+        <v>-2.604799174724169</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.2596302877691173</v>
+        <v>0.9637709366262793</v>
       </c>
       <c r="C27">
-        <v>0.6612568321875226</v>
+        <v>0.8233966905066528</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>1.789531928133219</v>
+        <v>1.308474321052123</v>
       </c>
       <c r="C28">
-        <v>0.9279994077673051</v>
+        <v>1.918393501834104</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>1.432915214409202</v>
+        <v>-0.6722359772212162</v>
       </c>
       <c r="C29">
-        <v>-0.4284605190128096</v>
+        <v>-2.349158231778473</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.4459260788700882</v>
+        <v>0.155680375204562</v>
       </c>
       <c r="C30">
-        <v>0.7408018169045668</v>
+        <v>1.318236985391727</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.9676881649455982</v>
+        <v>-0.968239711799267</v>
       </c>
       <c r="C31">
-        <v>0.2405141681281459</v>
+        <v>-0.3304198671478403</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.5924619781566037</v>
+        <v>-0.9926155544546639</v>
       </c>
       <c r="C32">
-        <v>0.8359283567958874</v>
+        <v>-2.270678335262473</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.563546297390534</v>
+        <v>-0.4907702891808756</v>
       </c>
       <c r="C33">
-        <v>0.9934160429345422</v>
+        <v>1.216589535287817</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.08344892357362063</v>
+        <v>1.301831638852421</v>
       </c>
       <c r="C34">
-        <v>-0.7131723300257843</v>
+        <v>-1.157390508981202</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-1.273451821930287</v>
+        <v>1.44806684055529</v>
       </c>
       <c r="C35">
-        <v>-0.2080452887271434</v>
+        <v>1.576995936206161</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-1.097450678193907</v>
+        <v>0.459297059920188</v>
       </c>
       <c r="C36">
-        <v>-1.637064161601637</v>
+        <v>0.6520089421539201</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-1.869486214645689</v>
+        <v>0.1817734369110262</v>
       </c>
       <c r="C37">
-        <v>0.2507127936285052</v>
+        <v>1.780949956629692</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.4240981333638603</v>
+        <v>-0.3037997963679923</v>
       </c>
       <c r="C38">
-        <v>-0.1953226957794661</v>
+        <v>-0.9430953964938381</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.2931715600670108</v>
+        <v>0.3228558146330719</v>
       </c>
       <c r="C39">
-        <v>-1.58448430056216</v>
+        <v>0.04703918068736171</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-1.268370455817347</v>
+        <v>0.9268990648202775</v>
       </c>
       <c r="C40">
-        <v>-0.2067523843075229</v>
+        <v>1.099118839646607</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.159634442384896</v>
+        <v>2.454856641751425</v>
       </c>
       <c r="C41">
-        <v>-1.258715920803061</v>
+        <v>2.184285211150485</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-1.166129040947409</v>
+        <v>-0.7937611665387545</v>
       </c>
       <c r="C42">
-        <v>-1.042341161234795</v>
+        <v>-0.368669901160689</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-1.411821877953637</v>
+        <v>-0.5102739273213124</v>
       </c>
       <c r="C43">
-        <v>-0.08918944496792008</v>
+        <v>-0.2074038057719971</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>1.362914986881642</v>
+        <v>-0.02700656849870115</v>
       </c>
       <c r="C44">
-        <v>-1.867578321111594</v>
+        <v>0.2155186131664975</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-1.11686858668926</v>
+        <v>0.748104677803537</v>
       </c>
       <c r="C45">
-        <v>2.203573996602382</v>
+        <v>-0.2274967508466506</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.1537882491806449</v>
+        <v>-0.7961336054096703</v>
       </c>
       <c r="C46">
-        <v>0.2823760113566683</v>
+        <v>-0.4519055915612614</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.09765084347983577</v>
+        <v>0.1152136928530658</v>
       </c>
       <c r="C47">
-        <v>-0.7069846972138786</v>
+        <v>0.1089468456168486</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-1.836795036837578</v>
+        <v>0.1140640542679855</v>
       </c>
       <c r="C48">
-        <v>2.01928614964558</v>
+        <v>0.7311715961915429</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-1.232121336858446</v>
+        <v>0.8232938960651952</v>
       </c>
       <c r="C49">
-        <v>-1.28044289803811</v>
+        <v>0.3942908570549832</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.5461613056244713</v>
+        <v>0.1041024153748257</v>
       </c>
       <c r="C50">
-        <v>-1.104708744100776</v>
+        <v>-0.006412348786677263</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>-0.01589530286627071</v>
+        <v>0.8898634189170191</v>
       </c>
       <c r="C51">
-        <v>-1.162763245384725</v>
+        <v>-0.1200044628360544</v>
       </c>
     </row>
     <row r="52">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>2.608247611871688</v>
+        <v>1.527743032076073</v>
       </c>
       <c r="C52">
-        <v>0.9782946089043393</v>
+        <v>0.01482273607679341</v>
       </c>
     </row>
     <row r="53">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>-0.1951187585928154</v>
+        <v>0.03420450829890073</v>
       </c>
       <c r="C53">
-        <v>-0.6277687700227712</v>
+        <v>-2.652677973265605</v>
       </c>
     </row>
     <row r="54">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>-0.8096328909057358</v>
+        <v>-0.6000262075667516</v>
       </c>
       <c r="C54">
-        <v>-0.5969806960622285</v>
+        <v>-0.3057563730821831</v>
       </c>
     </row>
     <row r="55">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>0.9377041156436047</v>
+        <v>-0.3133433317735686</v>
       </c>
       <c r="C55">
-        <v>1.600106614585954</v>
+        <v>-0.9173223218542383</v>
       </c>
     </row>
     <row r="56">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>0.1773269290867854</v>
+        <v>2.067889018711441</v>
       </c>
       <c r="C56">
-        <v>0.1796280300187478</v>
+        <v>1.103549736319339</v>
       </c>
     </row>
     <row r="57">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.04112726430146293</v>
+        <v>0.6672777171529617</v>
       </c>
       <c r="C57">
-        <v>-1.562099113241116</v>
+        <v>0.6902197196732716</v>
       </c>
     </row>
     <row r="58">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.5219179396987365</v>
+        <v>-0.9809956874766737</v>
       </c>
       <c r="C58">
-        <v>0.09199243677313741</v>
+        <v>-0.645457754076903</v>
       </c>
     </row>
     <row r="59">
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>1.43020140753429</v>
+        <v>-0.3643626327304574</v>
       </c>
       <c r="C59">
-        <v>-1.77379662661025</v>
+        <v>1.137102787450636</v>
       </c>
     </row>
     <row r="60">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>-0.976008096098019</v>
+        <v>0.07349141329374595</v>
       </c>
       <c r="C60">
-        <v>-0.6180407273347369</v>
+        <v>-0.5820416226511935</v>
       </c>
     </row>
     <row r="61">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>0.7384792002213787</v>
+        <v>0.2934798710465701</v>
       </c>
       <c r="C61">
-        <v>-0.6565607178416499</v>
+        <v>-0.2344144375324103</v>
       </c>
     </row>
     <row r="62">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>0.6151004962866378</v>
+        <v>-0.08716087601580151</v>
       </c>
       <c r="C62">
-        <v>1.050493137755608</v>
+        <v>-0.3214539439792273</v>
       </c>
     </row>
     <row r="63">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>-1.269258040137184</v>
+        <v>-1.917990833384273</v>
       </c>
       <c r="C63">
-        <v>-1.386412396486346</v>
+        <v>-0.897065528821127</v>
       </c>
     </row>
     <row r="64">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>0.6114258469624566</v>
+        <v>0.0594537014326986</v>
       </c>
       <c r="C64">
-        <v>0.1179434754117267</v>
+        <v>-0.9920783917842504</v>
       </c>
     </row>
     <row r="65">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>0.3281371909805706</v>
+        <v>-0.3487818870221642</v>
       </c>
       <c r="C65">
-        <v>-0.3847493744080722</v>
+        <v>1.707315476310696</v>
       </c>
     </row>
     <row r="66">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>0.254280565823973</v>
+        <v>0.8350235179256666</v>
       </c>
       <c r="C66">
-        <v>0.2571628291878313</v>
+        <v>1.092297190090846</v>
       </c>
     </row>
     <row r="67">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>1.424487137890816</v>
+        <v>-0.715823042063386</v>
       </c>
       <c r="C67">
-        <v>-0.2010993339628209</v>
+        <v>-0.8673320312796856</v>
       </c>
     </row>
     <row r="68">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>1.208505866344314</v>
+        <v>0.9697025601738395</v>
       </c>
       <c r="C68">
-        <v>-0.5531643190338426</v>
+        <v>1.001458746529136</v>
       </c>
     </row>
     <row r="69">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>-0.3580248264599306</v>
+        <v>1.224408962742622</v>
       </c>
       <c r="C69">
-        <v>-0.1740088198928054</v>
+        <v>-0.03101910113383149</v>
       </c>
     </row>
     <row r="70">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>-0.6665868827992705</v>
+        <v>0.7280831814931087</v>
       </c>
       <c r="C70">
-        <v>-0.02383341224828884</v>
+        <v>0.06237497491687224</v>
       </c>
     </row>
     <row r="71">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>-0.8770214254644788</v>
+        <v>-0.6521084872174484</v>
       </c>
       <c r="C71">
-        <v>-1.050481464877407</v>
+        <v>-0.06926764240110742</v>
       </c>
     </row>
     <row r="72">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>-0.1636576412392688</v>
+        <v>0.7951242891131225</v>
       </c>
       <c r="C72">
-        <v>-0.4043939215785267</v>
+        <v>3.337207431869757</v>
       </c>
     </row>
     <row r="73">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="B73">
-        <v>-0.8919890352832374</v>
+        <v>-1.023669194248929</v>
       </c>
       <c r="C73">
-        <v>3.400144264632663</v>
+        <v>-0.2146409399947364</v>
       </c>
     </row>
     <row r="74">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="B74">
-        <v>-1.128184891656395</v>
+        <v>1.762136333025494</v>
       </c>
       <c r="C74">
-        <v>-1.203940060151185</v>
+        <v>-1.045102167497502</v>
       </c>
     </row>
     <row r="75">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="B75">
-        <v>0.5483062775821732</v>
+        <v>0.4852339732350255</v>
       </c>
       <c r="C75">
-        <v>-1.13292480249906</v>
+        <v>-0.2437182189105316</v>
       </c>
     </row>
     <row r="76">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="B76">
-        <v>-1.246046210804546</v>
+        <v>-0.642024665073436</v>
       </c>
       <c r="C76">
-        <v>0.7189059357794366</v>
+        <v>-1.440592802068133</v>
       </c>
     </row>
     <row r="77">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>-0.08644102743693893</v>
+        <v>1.138617696052824</v>
       </c>
       <c r="C77">
-        <v>-0.2802821130392719</v>
+        <v>2.019133542878474</v>
       </c>
     </row>
     <row r="78">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>-0.1888677494603654</v>
+        <v>1.27807122068233</v>
       </c>
       <c r="C78">
-        <v>1.165409908760327</v>
+        <v>1.21222628896405</v>
       </c>
     </row>
     <row r="79">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>-0.4934402643193438</v>
+        <v>0.3031286013366233</v>
       </c>
       <c r="C79">
-        <v>0.9381572314546631</v>
+        <v>0.3102427441658392</v>
       </c>
     </row>
     <row r="80">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="B80">
-        <v>0.2925813561261903</v>
+        <v>0.9962537105962607</v>
       </c>
       <c r="C80">
-        <v>0.004230495772819216</v>
+        <v>0.9967240694674412</v>
       </c>
     </row>
     <row r="81">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B81">
-        <v>-1.132904313940494</v>
+        <v>-2.021579228602607</v>
       </c>
       <c r="C81">
-        <v>-0.8977784161524188</v>
+        <v>-1.315361277904877</v>
       </c>
     </row>
     <row r="82">
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="B82">
-        <v>-0.5916585399424533</v>
+        <v>1.361964445746158</v>
       </c>
       <c r="C82">
-        <v>-0.4874258985069552</v>
+        <v>0.2627123062667617</v>
       </c>
     </row>
     <row r="83">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="B83">
-        <v>-0.5912032475408282</v>
+        <v>-0.0266371100340646</v>
       </c>
       <c r="C83">
-        <v>0.5884649951118888</v>
+        <v>-0.2998631421481344</v>
       </c>
     </row>
     <row r="84">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>-1.611418885327743</v>
+        <v>1.17734338314916</v>
       </c>
       <c r="C84">
-        <v>0.2209701926022525</v>
+        <v>1.460606007472444</v>
       </c>
     </row>
     <row r="85">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="B85">
-        <v>-0.9616430542283075</v>
+        <v>-0.8855880896877204</v>
       </c>
       <c r="C85">
-        <v>-0.3127557156754361</v>
+        <v>0.2512632881904198</v>
       </c>
     </row>
     <row r="86">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="B86">
-        <v>-0.3943268237107285</v>
+        <v>0.2426832911650742</v>
       </c>
       <c r="C86">
-        <v>-0.9521224378665286</v>
+        <v>0.523269434414799</v>
       </c>
     </row>
     <row r="87">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="B87">
-        <v>-0.2430607802991926</v>
+        <v>0.4333496549641597</v>
       </c>
       <c r="C87">
-        <v>-0.1480637752128245</v>
+        <v>0.2260147895510743</v>
       </c>
     </row>
     <row r="88">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="B88">
-        <v>0.8181570875601353</v>
+        <v>0.7971971653632519</v>
       </c>
       <c r="C88">
-        <v>0.2244889969856139</v>
+        <v>-0.2171764721776762</v>
       </c>
     </row>
     <row r="89">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="B89">
-        <v>0.6837873306338352</v>
+        <v>-0.004271174708567932</v>
       </c>
       <c r="C89">
-        <v>-0.7212070974117686</v>
+        <v>-0.3514738961058189</v>
       </c>
     </row>
     <row r="90">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="B90">
-        <v>0.1780169807688258</v>
+        <v>-0.9665745069324624</v>
       </c>
       <c r="C90">
-        <v>-0.2686414890383068</v>
+        <v>0.3303067854435198</v>
       </c>
     </row>
     <row r="91">
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="B91">
-        <v>-0.3115789056635024</v>
+        <v>-1.261239127249802</v>
       </c>
       <c r="C91">
-        <v>-0.2419896215774264</v>
+        <v>0.141627138913806</v>
       </c>
     </row>
     <row r="92">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="B92">
-        <v>-0.9099189040376</v>
+        <v>-0.4749043174673484</v>
       </c>
       <c r="C92">
-        <v>-0.8674742771285446</v>
+        <v>-0.06256444498697614</v>
       </c>
     </row>
     <row r="93">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="B93">
-        <v>-0.7007120219243617</v>
+        <v>-1.440397840979432</v>
       </c>
       <c r="C93">
-        <v>-1.51985697877485</v>
+        <v>-0.2789408711039856</v>
       </c>
     </row>
     <row r="94">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B94">
-        <v>-0.4209930513975204</v>
+        <v>-0.3587314940000276</v>
       </c>
       <c r="C94">
-        <v>-0.0537728742362017</v>
+        <v>-0.2006335164417289</v>
       </c>
     </row>
     <row r="95">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B95">
-        <v>0.409647464965211</v>
+        <v>0.2893122224716633</v>
       </c>
       <c r="C95">
-        <v>0.5319167515864914</v>
+        <v>0.06102913634068161</v>
       </c>
     </row>
     <row r="96">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="B96">
-        <v>1.059436881541191</v>
+        <v>-0.005845072036752065</v>
       </c>
       <c r="C96">
-        <v>1.488327058143464</v>
+        <v>0.3193269667923198</v>
       </c>
     </row>
     <row r="97">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="B97">
-        <v>-0.916330464656845</v>
+        <v>-0.7964233051228318</v>
       </c>
       <c r="C97">
-        <v>-0.9802572826840084</v>
+        <v>-1.007357099858599</v>
       </c>
     </row>
     <row r="98">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="B98">
-        <v>-1.06873972532687</v>
+        <v>-1.317866575755713</v>
       </c>
       <c r="C98">
-        <v>0.268372470340394</v>
+        <v>-0.2986311015449882</v>
       </c>
     </row>
     <row r="99">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B99">
-        <v>-1.074993380828859</v>
+        <v>-2.011399174333483</v>
       </c>
       <c r="C99">
-        <v>0.1636043369580426</v>
+        <v>-0.9777320369627984</v>
       </c>
     </row>
     <row r="100">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="B100">
-        <v>1.36038520086727</v>
+        <v>-0.6981703317080346</v>
       </c>
       <c r="C100">
-        <v>2.32131696835754</v>
+        <v>-1.806860418317759</v>
       </c>
     </row>
     <row r="101">
@@ -1665,10 +1665,1310 @@
         </is>
       </c>
       <c r="B101">
-        <v>2.235973485446055</v>
+        <v>0.9664274666900704</v>
       </c>
       <c r="C101">
-        <v>1.810676746433172</v>
+        <v>0.2085345089528693</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>-1.436045331685682</v>
+      </c>
+      <c r="C102">
+        <v>-0.8458525032328676</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>1.860770001071881</v>
+      </c>
+      <c r="C103">
+        <v>-0.5195391081980061</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>-0.6053129944328193</v>
+      </c>
+      <c r="C104">
+        <v>0.5892052253573786</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>-0.5830774740214056</v>
+      </c>
+      <c r="C105">
+        <v>0.4243010688320027</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>1.321377345088909</v>
+      </c>
+      <c r="C106">
+        <v>0.6388002157128486</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>0.9839312868042809</v>
+      </c>
+      <c r="C107">
+        <v>1.061524030285796</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>-0.2448468678766517</v>
+      </c>
+      <c r="C108">
+        <v>0.07687777423472777</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>-0.2164381622583413</v>
+      </c>
+      <c r="C109">
+        <v>0.6262638058468373</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>-0.688618434996946</v>
+      </c>
+      <c r="C110">
+        <v>-2.238714394288396</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>-0.2572947079242563</v>
+      </c>
+      <c r="C111">
+        <v>1.972202769779687</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>-1.789545727077188</v>
+      </c>
+      <c r="C112">
+        <v>0.4562652041154155</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>0.3117411115993328</v>
+      </c>
+      <c r="C113">
+        <v>-0.008241047863395495</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>1.930790858655749</v>
+      </c>
+      <c r="C114">
+        <v>0.6087391050870582</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>-0.3465464832493883</v>
+      </c>
+      <c r="C115">
+        <v>0.3577420922369832</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>0.5807462928289403</v>
+      </c>
+      <c r="C116">
+        <v>-0.1862322350850256</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>-0.3697005494232993</v>
+      </c>
+      <c r="C117">
+        <v>-0.820980723919646</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>0.6615758926730794</v>
+      </c>
+      <c r="C118">
+        <v>-1.037071344671152</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>0.4405778855485986</v>
+      </c>
+      <c r="C119">
+        <v>-1.512632342681158</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>1.846297114799559</v>
+      </c>
+      <c r="C120">
+        <v>1.38177893530427</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>-0.4706201885602668</v>
+      </c>
+      <c r="C121">
+        <v>0.7214168771811492</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>-0.8712163042016808</v>
+      </c>
+      <c r="C122">
+        <v>0.723103651299581</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>1.181873823245789</v>
+      </c>
+      <c r="C123">
+        <v>2.397323407421466</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>0.03896124402900032</v>
+      </c>
+      <c r="C124">
+        <v>-1.049515327111079</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>-0.9388018157358338</v>
+      </c>
+      <c r="C125">
+        <v>-1.459318754074051</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>-0.4563950244882855</v>
+      </c>
+      <c r="C126">
+        <v>-0.2675677629826838</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>1.49786321701003</v>
+      </c>
+      <c r="C127">
+        <v>0.9199027969038751</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>0.3387578257476467</v>
+      </c>
+      <c r="C128">
+        <v>0.116276888615447</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>-0.7689418948159347</v>
+      </c>
+      <c r="C129">
+        <v>-0.5175508443342365</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>-0.6338850026383545</v>
+      </c>
+      <c r="C130">
+        <v>1.608489287169854</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>1.856953422422398</v>
+      </c>
+      <c r="C131">
+        <v>1.770365677255618</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>0.3863695577667177</v>
+      </c>
+      <c r="C132">
+        <v>0.5147196096497358</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>0.2717730752112337</v>
+      </c>
+      <c r="C133">
+        <v>-0.6193338964746098</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>1.909231039150593</v>
+      </c>
+      <c r="C134">
+        <v>0.7298596567824825</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>0.1793748494858961</v>
+      </c>
+      <c r="C135">
+        <v>0.4184995775315538</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>-0.06570110168297669</v>
+      </c>
+      <c r="C136">
+        <v>0.9790054137510218</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>-0.05165535370631186</v>
+      </c>
+      <c r="C137">
+        <v>0.2103606216685453</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>0.3458333452620815</v>
+      </c>
+      <c r="C138">
+        <v>0.1697799187421886</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>0.8990161898686505</v>
+      </c>
+      <c r="C139">
+        <v>0.06100680036525241</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>-0.1130633918010226</v>
+      </c>
+      <c r="C140">
+        <v>1.074860386774205</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>-1.162464125891809</v>
+      </c>
+      <c r="C141">
+        <v>0.7879459798090314</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>-1.799219038187084</v>
+      </c>
+      <c r="C142">
+        <v>0.169644725275191</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>0.8495433675846806</v>
+      </c>
+      <c r="C143">
+        <v>-1.362366253164255</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>0.1345019171835562</v>
+      </c>
+      <c r="C144">
+        <v>0.05256464684185018</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>-1.737926359920215</v>
+      </c>
+      <c r="C145">
+        <v>-1.52948055479609</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>1.742028717286339</v>
+      </c>
+      <c r="C146">
+        <v>0.4714072251017818</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>-0.4201859426065653</v>
+      </c>
+      <c r="C147">
+        <v>-0.39420401371798</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>0.8035901832775609</v>
+      </c>
+      <c r="C148">
+        <v>0.6835867370825255</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>-0.1695418824188581</v>
+      </c>
+      <c r="C149">
+        <v>1.410930927760432</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>0.09236945563616644</v>
+      </c>
+      <c r="C150">
+        <v>0.07193754156785538</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>-0.7732464953884441</v>
+      </c>
+      <c r="C151">
+        <v>-0.9518714546944025</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>1.464530684742658</v>
+      </c>
+      <c r="C152">
+        <v>-0.1441071327610977</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>-0.6839481330625456</v>
+      </c>
+      <c r="C153">
+        <v>-3.003987567727747</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>-1.317346931371674</v>
+      </c>
+      <c r="C154">
+        <v>-0.2662753833136659</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>-0.3252364022838942</v>
+      </c>
+      <c r="C155">
+        <v>1.459344666330299</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>1.284704798665952</v>
+      </c>
+      <c r="C156">
+        <v>2.648917938302778</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>-0.4856260119182735</v>
+      </c>
+      <c r="C157">
+        <v>0.9311250222515782</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>0.8613222402459709</v>
+      </c>
+      <c r="C158">
+        <v>0.10213863187419</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>-0.3646546923216573</v>
+      </c>
+      <c r="C159">
+        <v>-0.7261307281673276</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>0.1478920268272159</v>
+      </c>
+      <c r="C160">
+        <v>-0.1443953913818724</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>0.4957835691282454</v>
+      </c>
+      <c r="C161">
+        <v>-0.5248806726495494</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>-1.260648140226795</v>
+      </c>
+      <c r="C162">
+        <v>-1.673055243176513</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>0.1927309676951038</v>
+      </c>
+      <c r="C163">
+        <v>0.400261690928498</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>0.6911241740765639</v>
+      </c>
+      <c r="C164">
+        <v>-0.2296827600209477</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>0.3380172456196355</v>
+      </c>
+      <c r="C165">
+        <v>0.06001958627311667</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>-0.5765038844218602</v>
+      </c>
+      <c r="C166">
+        <v>-0.6911699909917425</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>1.065442728023679</v>
+      </c>
+      <c r="C167">
+        <v>0.4689767726291766</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>-1.116738624539876</v>
+      </c>
+      <c r="C168">
+        <v>0.5041178347668663</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>-0.2015991823256483</v>
+      </c>
+      <c r="C169">
+        <v>0.0562850509113679</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>-1.416721121919628</v>
+      </c>
+      <c r="C170">
+        <v>-0.712518865155903</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>1.374236736131129</v>
+      </c>
+      <c r="C171">
+        <v>1.361990863198622</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>0.2270603822048829</v>
+      </c>
+      <c r="C172">
+        <v>-0.6301038624951256</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>0.4180316399418338</v>
+      </c>
+      <c r="C173">
+        <v>0.8639379109820122</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>0.04613393061904095</v>
+      </c>
+      <c r="C174">
+        <v>0.001971344184228278</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>0.9022252376018952</v>
+      </c>
+      <c r="C175">
+        <v>0.6501385100319841</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>0.822073665055212</v>
+      </c>
+      <c r="C176">
+        <v>-1.662676857243137</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>0.5901427114212037</v>
+      </c>
+      <c r="C177">
+        <v>-0.2927132179635433</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>2.37260425938728</v>
+      </c>
+      <c r="C178">
+        <v>0.172595722686444</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>0.8736940164246185</v>
+      </c>
+      <c r="C179">
+        <v>-0.4745378026490413</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>0.3260275373779968</v>
+      </c>
+      <c r="C180">
+        <v>1.707593767483136</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>1.181064083945362</v>
+      </c>
+      <c r="C181">
+        <v>0.1073599758854449</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>-0.631705783214385</v>
+      </c>
+      <c r="C182">
+        <v>0.7247754902830641</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>-0.9516634512196336</v>
+      </c>
+      <c r="C183">
+        <v>-0.5036869544078268</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>-1.372286058633891</v>
+      </c>
+      <c r="C184">
+        <v>-0.6588392420892446</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>0.5280949716552987</v>
+      </c>
+      <c r="C185">
+        <v>-0.9003320064446766</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>-0.8990322779748027</v>
+      </c>
+      <c r="C186">
+        <v>-0.8323630465306597</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>-0.373199863182389</v>
+      </c>
+      <c r="C187">
+        <v>-0.04114267715184787</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>-0.2587485687475</v>
+      </c>
+      <c r="C188">
+        <v>-0.3237484602925977</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>1.301042918453001</v>
+      </c>
+      <c r="C189">
+        <v>0.5744600528083147</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>1.7620570107628</v>
+      </c>
+      <c r="C190">
+        <v>-0.4641137914803896</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>-0.9844157175202153</v>
+      </c>
+      <c r="C191">
+        <v>-1.454137732297564</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>-0.215540548519037</v>
+      </c>
+      <c r="C192">
+        <v>0.5260393576138578</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>-0.174560329173698</v>
+      </c>
+      <c r="C193">
+        <v>-0.3235762049057351</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>1.606321044426813</v>
+      </c>
+      <c r="C194">
+        <v>-1.40836322869397</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>-0.6310609846146449</v>
+      </c>
+      <c r="C195">
+        <v>-1.513995584920332</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>0.03234785446410812</v>
+      </c>
+      <c r="C196">
+        <v>-1.135344410685841</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>1.970328793125462</v>
+      </c>
+      <c r="C197">
+        <v>0.984356331511011</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>0.1901356954070757</v>
+      </c>
+      <c r="C198">
+        <v>-1.336881048780504</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>-1.009481351500465</v>
+      </c>
+      <c r="C199">
+        <v>0.6710343654794825</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>-1.305198400794173</v>
+      </c>
+      <c r="C200">
+        <v>-0.7100711011661098</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>-2.859494372887019</v>
+      </c>
+      <c r="C201">
+        <v>-0.6466094382207588</v>
       </c>
     </row>
   </sheetData>
